--- a/basedatos_partidas/salida/descompuestos/CT-18-05-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-05-010.xlsx
@@ -539,10 +539,10 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="n">
-        <v>17.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13">
@@ -617,10 +617,10 @@
         <v>0.02</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="14">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>28.05</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="17">
@@ -782,10 +782,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>36.9</v>
+        <v>29.22</v>
       </c>
       <c r="H22" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="23">
@@ -801,7 +801,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>37.27</v>
+        <v>29.51</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-18-05-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-05-010.xlsx
@@ -643,10 +643,10 @@
         <v>0.2</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="15">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="G15" t="n">
-        <v>8.5</v>
+        <v>32</v>
       </c>
       <c r="H15" t="n">
-        <v>0.51</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>20.37</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="17">
@@ -782,10 +782,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>29.22</v>
+        <v>30.89</v>
       </c>
       <c r="H22" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="23">
@@ -801,7 +801,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>29.51</v>
+        <v>31.2</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-18-05-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-05-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 18 Obras exteriores y urbanismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Instalaciones exteriores</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
